--- a/Data/Grid.xlsx
+++ b/Data/Grid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liron\UnityProjects\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3C8729-650D-4790-B6A7-04906952A768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A8C5B1-B3E2-4D06-BAE4-58A59D30D3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{29EEFF8D-8DCA-432E-94A7-224158E5361E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="203">
   <si>
     <t>S1</t>
   </si>
@@ -4126,14 +4126,11 @@
       <c r="D29" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>148</v>
+      <c r="G29" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>151</v>
@@ -4145,19 +4142,19 @@
         <v>151</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>148</v>
+        <v>148</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S29" s="2" t="s">
         <v>147</v>
@@ -4201,26 +4198,29 @@
         <v>151</v>
       </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="G30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>148</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>148</v>
+      <c r="M30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>147</v>
@@ -4264,37 +4264,41 @@
         <v>151</v>
       </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G31" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I31" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="K31" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K31" s="17"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="6" t="s">
+      <c r="L31" s="6" t="s">
         <v>1</v>
       </c>
+      <c r="M31" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N31" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>147</v>
@@ -4338,38 +4342,39 @@
         <v>151</v>
       </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J32" s="19"/>
       <c r="K32" s="20"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O32" s="5" t="s">
+      <c r="M32" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N32" s="5" t="s">
         <v>129</v>
       </c>
+      <c r="O32" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P32" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>147</v>
@@ -4413,38 +4418,39 @@
         <v>151</v>
       </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G33" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I33" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J33" s="19"/>
       <c r="K33" s="20"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="M33" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N33" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>147</v>
@@ -4482,38 +4488,39 @@
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="E34" s="42"/>
-      <c r="F34" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J34" s="19"/>
       <c r="K34" s="20"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N34" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O34" s="5" t="s">
+      <c r="M34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N34" s="5" t="s">
         <v>130</v>
       </c>
+      <c r="O34" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P34" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>147</v>
@@ -4549,38 +4556,39 @@
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
       <c r="E35" s="43"/>
-      <c r="F35" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G35" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="19"/>
       <c r="K35" s="20"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="M35" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N35" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S35" s="2" t="s">
         <v>147</v>
@@ -4616,38 +4624,39 @@
       <c r="C36" s="33"/>
       <c r="D36" s="33"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J36" s="19"/>
       <c r="K36" s="20"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="11" t="s">
+      <c r="L36" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O36" s="5" t="s">
+      <c r="M36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N36" s="5" t="s">
         <v>131</v>
       </c>
+      <c r="O36" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P36" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S36" s="2" t="s">
         <v>147</v>
@@ -4683,38 +4692,39 @@
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
       <c r="E37" s="43"/>
-      <c r="F37" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I37" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="19"/>
       <c r="K37" s="20"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="11" t="s">
+      <c r="L37" s="11" t="s">
         <v>13</v>
       </c>
+      <c r="M37" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N37" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>147</v>
@@ -4750,38 +4760,39 @@
       <c r="C38" s="33"/>
       <c r="D38" s="33"/>
       <c r="E38" s="43"/>
-      <c r="F38" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J38" s="19"/>
       <c r="K38" s="20"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="11" t="s">
+      <c r="L38" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O38" s="5" t="s">
+      <c r="M38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N38" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="O38" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P38" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>147</v>
@@ -4817,38 +4828,39 @@
       <c r="C39" s="33"/>
       <c r="D39" s="33"/>
       <c r="E39" s="43"/>
-      <c r="F39" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I39" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J39" s="19"/>
       <c r="K39" s="20"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="M39" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N39" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>147</v>
@@ -4884,38 +4896,39 @@
       <c r="C40" s="33"/>
       <c r="D40" s="33"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="19"/>
       <c r="K40" s="20"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="10" t="s">
+      <c r="L40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O40" s="5" t="s">
+      <c r="M40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N40" s="5" t="s">
         <v>133</v>
       </c>
+      <c r="O40" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S40" s="2" t="s">
         <v>147</v>
@@ -4951,38 +4964,39 @@
       <c r="C41" s="33"/>
       <c r="D41" s="33"/>
       <c r="E41" s="43"/>
-      <c r="F41" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G41" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J41" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J41" s="19"/>
       <c r="K41" s="20"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="10" t="s">
+      <c r="L41" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="M41" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N41" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S41" s="2" t="s">
         <v>147</v>
@@ -5018,38 +5032,39 @@
       <c r="C42" s="33"/>
       <c r="D42" s="33"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I42" s="10" t="s">
+      <c r="I42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J42" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="19"/>
       <c r="K42" s="20"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="10" t="s">
+      <c r="L42" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O42" s="5" t="s">
+      <c r="M42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N42" s="5" t="s">
         <v>134</v>
       </c>
+      <c r="O42" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P42" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S42" s="2" t="s">
         <v>147</v>
@@ -5085,38 +5100,39 @@
       <c r="C43" s="33"/>
       <c r="D43" s="33"/>
       <c r="E43" s="43"/>
-      <c r="F43" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I43" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="19"/>
       <c r="K43" s="20"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="10" t="s">
+      <c r="L43" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="M43" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="N43" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>147</v>
@@ -5152,38 +5168,39 @@
       <c r="C44" s="33"/>
       <c r="D44" s="33"/>
       <c r="E44" s="43"/>
-      <c r="F44" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J44" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="22"/>
       <c r="K44" s="23"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="10" t="s">
+      <c r="L44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="O44" s="5" t="s">
+      <c r="M44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N44" s="5" t="s">
         <v>135</v>
       </c>
+      <c r="O44" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P44" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>147</v>
@@ -5227,14 +5244,17 @@
       <c r="N45" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O45" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P45" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>147</v>
@@ -5276,14 +5296,17 @@
       <c r="N46" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O46" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P46" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S46" s="2" t="s">
         <v>147</v>
@@ -5328,14 +5351,17 @@
       <c r="N47" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O47" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P47" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>147</v>
@@ -5380,14 +5406,17 @@
       <c r="N48" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O48" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>147</v>
@@ -5432,14 +5461,17 @@
       <c r="N49" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O49" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P49" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>147</v>
@@ -5484,14 +5516,17 @@
       <c r="N50" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O50" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>147</v>
@@ -5536,14 +5571,17 @@
       <c r="N51" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O51" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P51" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>147</v>
@@ -5588,14 +5626,17 @@
       <c r="N52" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O52" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>147</v>
@@ -5643,14 +5684,17 @@
       <c r="N53" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O53" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>141</v>
@@ -5696,14 +5740,17 @@
       <c r="N54" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="O54" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P54" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>142</v>
@@ -5805,7 +5852,7 @@
       <c r="J56" s="40"/>
       <c r="K56" s="40"/>
       <c r="L56" s="41"/>
-      <c r="M56" s="9" t="s">
+      <c r="M56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="N56" s="6" t="s">
@@ -5853,11 +5900,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="J31:L44"/>
     <mergeCell ref="J45:L52"/>
     <mergeCell ref="I53:L56"/>
     <mergeCell ref="A34:E56"/>
     <mergeCell ref="F47:H56"/>
+    <mergeCell ref="K31:K44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
